--- a/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_12.xlsx
+++ b/Res_ConvLSTM/DroughtDataset_model_testing_1755095296_individual_h_12.xlsx
@@ -658,7 +658,7 @@
         <v>0.008566648607316726</v>
       </c>
       <c r="C2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -679,49 +679,49 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="K2" t="n">
-        <v>52039233</v>
+        <v>4235978</v>
       </c>
       <c r="L2" t="n">
-        <v>26539396</v>
+        <v>1319346</v>
       </c>
       <c r="M2" t="n">
-        <v>6029428</v>
+        <v>242849</v>
       </c>
       <c r="N2" t="n">
-        <v>253928</v>
+        <v>5764</v>
       </c>
       <c r="O2" t="n">
-        <v>3599910</v>
+        <v>188027</v>
       </c>
       <c r="P2" t="n">
-        <v>1278584</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.9999366998672485</v>
+        <v>0.9999341368675232</v>
       </c>
       <c r="R2" t="n">
-        <v>0.816702663898468</v>
+        <v>0.6741712093353271</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6913463473320007</v>
+        <v>0.5279875993728638</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6167545318603516</v>
+        <v>0.3885447084903717</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2073727995157242</v>
+        <v>0.04465378448367119</v>
       </c>
       <c r="V2" t="n">
-        <v>0.6547884941101074</v>
+        <v>0.3918772041797638</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8043422102928162</v>
+        <v>0.1459227502346039</v>
       </c>
       <c r="X2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
@@ -742,46 +742,46 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>75755736</v>
+        <v>6312978</v>
       </c>
       <c r="AF2" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="AG2" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AH2" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AI2" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AJ2" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AK2" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AL2" t="n">
         <v>1</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.9556694626808167</v>
+        <v>0.9541478753089905</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.9118999242782593</v>
+        <v>0.9129630327224731</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.8581674098968506</v>
+        <v>0.8576433062553406</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.6615565419197083</v>
+        <v>0.6601934432983398</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9019808769226074</v>
+        <v>0.9016708135604858</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.9314422011375427</v>
+        <v>0.9313058257102966</v>
       </c>
     </row>
     <row r="3">
@@ -792,130 +792,130 @@
         <v>0.002053537536211935</v>
       </c>
       <c r="C3" t="n">
-        <v>3540</v>
+        <v>392</v>
       </c>
       <c r="D3" t="n">
-        <v>52039233</v>
+        <v>4235978</v>
       </c>
       <c r="E3" t="n">
-        <v>7625285</v>
+        <v>645756</v>
       </c>
       <c r="F3" t="n">
-        <v>238389</v>
+        <v>35789</v>
       </c>
       <c r="G3" t="n">
-        <v>20847</v>
+        <v>4348</v>
       </c>
       <c r="H3" t="n">
-        <v>19948</v>
+        <v>6214</v>
       </c>
       <c r="I3" t="n">
-        <v>964</v>
+        <v>33</v>
       </c>
       <c r="J3" t="n">
-        <v>120194670</v>
+        <v>10016206</v>
       </c>
       <c r="K3" t="n">
-        <v>124327528</v>
+        <v>9353830</v>
       </c>
       <c r="L3" t="n">
-        <v>144619303</v>
+        <v>11804658</v>
       </c>
       <c r="M3" t="n">
-        <v>180966730</v>
+        <v>15001896</v>
       </c>
       <c r="N3" t="n">
-        <v>193911035</v>
+        <v>16116213</v>
       </c>
       <c r="O3" t="n">
-        <v>187931362</v>
+        <v>15524822</v>
       </c>
       <c r="P3" t="n">
-        <v>193321587</v>
+        <v>16135351</v>
       </c>
       <c r="Q3" t="n">
         <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8680698871612549</v>
+        <v>0.8594844937324524</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6720994710922241</v>
+        <v>0.3943681418895721</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5363381505012512</v>
+        <v>0.2568387389183044</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2365216612815857</v>
+        <v>0.06399538367986679</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5876514911651611</v>
+        <v>0.3665286600589752</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5504980683326721</v>
+        <v>0.0001752125681377947</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>57400955</v>
+        <v>4717265</v>
       </c>
       <c r="Z3" t="n">
-        <v>2363094</v>
+        <v>195844</v>
       </c>
       <c r="AA3" t="n">
-        <v>101765</v>
+        <v>8538</v>
       </c>
       <c r="AB3" t="n">
-        <v>81730</v>
+        <v>6822</v>
       </c>
       <c r="AC3" t="n">
-        <v>302</v>
+        <v>11</v>
       </c>
       <c r="AD3" t="n">
-        <v>360</v>
+        <v>30</v>
       </c>
       <c r="AE3" t="n">
-        <v>120199464</v>
+        <v>10016622</v>
       </c>
       <c r="AF3" t="n">
-        <v>133344343</v>
+        <v>11174399</v>
       </c>
       <c r="AG3" t="n">
-        <v>152997368</v>
+        <v>12694080</v>
       </c>
       <c r="AH3" t="n">
-        <v>183120991</v>
+        <v>15249719</v>
       </c>
       <c r="AI3" t="n">
-        <v>194518645</v>
+        <v>16208962</v>
       </c>
       <c r="AJ3" t="n">
-        <v>189229252</v>
+        <v>15766212</v>
       </c>
       <c r="AK3" t="n">
-        <v>193473427</v>
+        <v>16122228</v>
       </c>
       <c r="AL3" t="n">
         <v>1</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.9575091600418091</v>
+        <v>0.9571381807327271</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.9097229242324829</v>
+        <v>0.9094282388687134</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.8570423722267151</v>
+        <v>0.8560332655906677</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.6608491539955139</v>
+        <v>0.6593944430351257</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.9013246297836304</v>
+        <v>0.900807797908783</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.931126594543457</v>
+        <v>0.9307395219802856</v>
       </c>
     </row>
     <row r="4">
@@ -926,285 +926,285 @@
         <v>0.03228002292548469</v>
       </c>
       <c r="C4" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>10652475</v>
+        <v>1787264</v>
       </c>
       <c r="E4" t="n">
-        <v>26539396</v>
+        <v>1319346</v>
       </c>
       <c r="F4" t="n">
-        <v>1906955</v>
+        <v>171608</v>
       </c>
       <c r="G4" t="n">
-        <v>132379</v>
+        <v>22745</v>
       </c>
       <c r="H4" t="n">
-        <v>237634</v>
+        <v>44487</v>
       </c>
       <c r="I4" t="n">
-        <v>18355</v>
+        <v>18</v>
       </c>
       <c r="J4" t="n">
-        <v>4794</v>
+        <v>416</v>
       </c>
       <c r="K4" t="n">
-        <v>11679466</v>
+        <v>2047260</v>
       </c>
       <c r="L4" t="n">
-        <v>11848594</v>
+        <v>1179474</v>
       </c>
       <c r="M4" t="n">
-        <v>3746630</v>
+        <v>382173</v>
       </c>
       <c r="N4" t="n">
-        <v>970572</v>
+        <v>123318</v>
       </c>
       <c r="O4" t="n">
-        <v>1897911</v>
+        <v>291784</v>
       </c>
       <c r="P4" t="n">
-        <v>311018</v>
+        <v>199</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.9999683499336243</v>
+        <v>0.9999670386314392</v>
       </c>
       <c r="R4" t="n">
-        <v>0.8416032195091248</v>
+        <v>0.7556321024894714</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6815871000289917</v>
+        <v>0.4514993131160736</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5737422704696655</v>
+        <v>0.3092528283596039</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2209901958703995</v>
+        <v>0.05260299891233444</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6194061040878296</v>
+        <v>0.3787793219089508</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6536399126052856</v>
+        <v>0.0003500049060676247</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>2487043</v>
+        <v>211876</v>
       </c>
       <c r="Z4" t="n">
-        <v>35922504</v>
+        <v>3042463</v>
       </c>
       <c r="AA4" t="n">
-        <v>996591</v>
+        <v>84107</v>
       </c>
       <c r="AB4" t="n">
-        <v>66559</v>
+        <v>5676</v>
       </c>
       <c r="AC4" t="n">
-        <v>13785</v>
+        <v>1273</v>
       </c>
       <c r="AD4" t="n">
-        <v>821</v>
+        <v>73</v>
       </c>
       <c r="AE4" t="n">
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>2662651</v>
+        <v>226691</v>
       </c>
       <c r="AG4" t="n">
-        <v>3470529</v>
+        <v>290052</v>
       </c>
       <c r="AH4" t="n">
-        <v>1592369</v>
+        <v>134350</v>
       </c>
       <c r="AI4" t="n">
-        <v>362962</v>
+        <v>30569</v>
       </c>
       <c r="AJ4" t="n">
-        <v>600021</v>
+        <v>50394</v>
       </c>
       <c r="AK4" t="n">
-        <v>159178</v>
+        <v>13322</v>
       </c>
       <c r="AL4" t="n">
         <v>1</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.9565883874893188</v>
+        <v>0.9556406140327454</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.910810112953186</v>
+        <v>0.9111921787261963</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.8576045632362366</v>
+        <v>0.8568375706672668</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.6612026691436768</v>
+        <v>0.6597936749458313</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.9016525745391846</v>
+        <v>0.9012390971183777</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.9312843680381775</v>
+        <v>0.931022584438324</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr"/>
       <c r="C5" t="n">
-        <v>630</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>737468</v>
+        <v>189971</v>
       </c>
       <c r="E5" t="n">
-        <v>3366569</v>
+        <v>383820</v>
       </c>
       <c r="F5" t="n">
-        <v>6029428</v>
+        <v>242849</v>
       </c>
       <c r="G5" t="n">
-        <v>294111</v>
+        <v>34786</v>
       </c>
       <c r="H5" t="n">
-        <v>746208</v>
+        <v>94065</v>
       </c>
       <c r="I5" t="n">
-        <v>67426</v>
+        <v>40</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>7908973</v>
+        <v>692532</v>
       </c>
       <c r="L5" t="n">
-        <v>12947907</v>
+        <v>2026122</v>
       </c>
       <c r="M5" t="n">
-        <v>5212412</v>
+        <v>702682</v>
       </c>
       <c r="N5" t="n">
-        <v>819665</v>
+        <v>84305</v>
       </c>
       <c r="O5" t="n">
-        <v>2526017</v>
+        <v>324967</v>
       </c>
       <c r="P5" t="n">
-        <v>1044011</v>
+        <v>194016</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9999755620956421</v>
+        <v>0.9999745488166809</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9000361561775208</v>
+        <v>0.8322193026542664</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8734583258628845</v>
+        <v>0.8036941289901733</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9542801380157471</v>
+        <v>0.9335651397705078</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9908640384674072</v>
+        <v>0.9872854948043823</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9774237871170044</v>
+        <v>0.9622310996055603</v>
       </c>
       <c r="W5" t="n">
-        <v>0.9930850267410278</v>
+        <v>0.9881065487861633</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>96751</v>
+        <v>8160</v>
       </c>
       <c r="Z5" t="n">
-        <v>1032439</v>
+        <v>87923</v>
       </c>
       <c r="AA5" t="n">
-        <v>9634733</v>
+        <v>809406</v>
       </c>
       <c r="AB5" t="n">
-        <v>119853</v>
+        <v>10057</v>
       </c>
       <c r="AC5" t="n">
-        <v>350460</v>
+        <v>29344</v>
       </c>
       <c r="AD5" t="n">
-        <v>7604</v>
+        <v>641</v>
       </c>
       <c r="AE5" t="n">
         <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>2547251</v>
+        <v>211245</v>
       </c>
       <c r="AG5" t="n">
-        <v>3564799</v>
+        <v>303005</v>
       </c>
       <c r="AH5" t="n">
-        <v>1607107</v>
+        <v>136125</v>
       </c>
       <c r="AI5" t="n">
-        <v>364110</v>
+        <v>30678</v>
       </c>
       <c r="AJ5" t="n">
-        <v>604478</v>
+        <v>50885</v>
       </c>
       <c r="AK5" t="n">
-        <v>159965</v>
+        <v>13440</v>
       </c>
       <c r="AL5" t="n">
         <v>1</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.973412811756134</v>
+        <v>0.9731814861297607</v>
       </c>
       <c r="AN5" t="n">
-        <v>0.964097261428833</v>
+        <v>0.9636821150779724</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.9836724400520325</v>
+        <v>0.9834365248680115</v>
       </c>
       <c r="AP5" t="n">
-        <v>0.9962896108627319</v>
+        <v>0.9962493181228638</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0.9938532114028931</v>
+        <v>0.9937978386878967</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.9983713626861572</v>
+        <v>0.9983611106872559</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="n">
-        <v>262</v>
+        <v>23</v>
       </c>
       <c r="D6" t="n">
-        <v>192940</v>
+        <v>30568</v>
       </c>
       <c r="E6" t="n">
-        <v>244160</v>
+        <v>24009</v>
       </c>
       <c r="F6" t="n">
-        <v>268616</v>
+        <v>19955</v>
       </c>
       <c r="G6" t="n">
-        <v>253928</v>
+        <v>5764</v>
       </c>
       <c r="H6" t="n">
-        <v>104400</v>
+        <v>9731</v>
       </c>
       <c r="I6" t="n">
-        <v>9287</v>
+        <v>19</v>
       </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -1224,22 +1224,22 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>78306</v>
+        <v>6619</v>
       </c>
       <c r="Z6" t="n">
-        <v>64303</v>
+        <v>5393</v>
       </c>
       <c r="AA6" t="n">
-        <v>131730</v>
+        <v>11143</v>
       </c>
       <c r="AB6" t="n">
-        <v>709483</v>
+        <v>59391</v>
       </c>
       <c r="AC6" t="n">
-        <v>83993</v>
+        <v>7037</v>
       </c>
       <c r="AD6" t="n">
-        <v>5778</v>
+        <v>486</v>
       </c>
       <c r="AE6" t="inlineStr"/>
       <c r="AF6" t="inlineStr"/>
@@ -1260,25 +1260,25 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr"/>
       <c r="C7" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>88831</v>
+        <v>35378</v>
       </c>
       <c r="E7" t="n">
-        <v>555236</v>
+        <v>111448</v>
       </c>
       <c r="F7" t="n">
-        <v>1210000</v>
+        <v>129539</v>
       </c>
       <c r="G7" t="n">
-        <v>456904</v>
+        <v>48512</v>
       </c>
       <c r="H7" t="n">
-        <v>3599910</v>
+        <v>188027</v>
       </c>
       <c r="I7" t="n">
-        <v>214986</v>
+        <v>89</v>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -1298,22 +1298,22 @@
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>215</v>
+        <v>8</v>
       </c>
       <c r="Z7" t="n">
-        <v>9720</v>
+        <v>810</v>
       </c>
       <c r="AA7" t="n">
-        <v>358302</v>
+        <v>30228</v>
       </c>
       <c r="AB7" t="n">
-        <v>91626</v>
+        <v>7747</v>
       </c>
       <c r="AC7" t="n">
-        <v>5521449</v>
+        <v>462109</v>
       </c>
       <c r="AD7" t="n">
-        <v>144615</v>
+        <v>12092</v>
       </c>
       <c r="AE7" t="inlineStr"/>
       <c r="AF7" t="inlineStr"/>
@@ -1334,25 +1334,25 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr"/>
       <c r="C8" t="n">
-        <v>193</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>7752</v>
+        <v>4079</v>
       </c>
       <c r="E8" t="n">
-        <v>57344</v>
+        <v>14441</v>
       </c>
       <c r="F8" t="n">
-        <v>122670</v>
+        <v>25282</v>
       </c>
       <c r="G8" t="n">
-        <v>66331</v>
+        <v>12927</v>
       </c>
       <c r="H8" t="n">
-        <v>789721</v>
+        <v>137287</v>
       </c>
       <c r="I8" t="n">
-        <v>1278584</v>
+        <v>34</v>
       </c>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -1372,22 +1372,22 @@
         <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>336</v>
+        <v>28</v>
       </c>
       <c r="Z8" t="n">
-        <v>973</v>
+        <v>82</v>
       </c>
       <c r="AA8" t="n">
-        <v>3981</v>
+        <v>334</v>
       </c>
       <c r="AB8" t="n">
-        <v>3194</v>
+        <v>267</v>
       </c>
       <c r="AC8" t="n">
-        <v>151481</v>
+        <v>12729</v>
       </c>
       <c r="AD8" t="n">
-        <v>2162630</v>
+        <v>180610</v>
       </c>
       <c r="AE8" t="inlineStr"/>
       <c r="AF8" t="inlineStr"/>
